--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30890,6 +30890,117 @@
       <c r="A269" s="1" t="n">
         <v>46281</v>
       </c>
+      <c r="B269" t="n">
+        <v>14326046.43101005</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" t="n">
+        <v>74</v>
+      </c>
+      <c r="G269" t="n">
+        <v>4</v>
+      </c>
+      <c r="H269" t="n">
+        <v>2</v>
+      </c>
+      <c r="I269" t="n">
+        <v>23</v>
+      </c>
+      <c r="J269" t="n">
+        <v>9</v>
+      </c>
+      <c r="K269" t="n">
+        <v>2</v>
+      </c>
+      <c r="L269" t="n">
+        <v>3</v>
+      </c>
+      <c r="M269" t="n">
+        <v>4</v>
+      </c>
+      <c r="N269" t="n">
+        <v>4</v>
+      </c>
+      <c r="O269" t="n">
+        <v>3</v>
+      </c>
+      <c r="P269" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>11</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2</v>
+      </c>
+      <c r="S269" t="n">
+        <v>11</v>
+      </c>
+      <c r="T269" t="n">
+        <v>16</v>
+      </c>
+      <c r="U269" t="n">
+        <v>3</v>
+      </c>
+      <c r="V269" t="n">
+        <v>0</v>
+      </c>
+      <c r="W269" t="n">
+        <v>3</v>
+      </c>
+      <c r="X269" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31006,6 +31006,117 @@
       <c r="A270" s="1" t="n">
         <v>46282</v>
       </c>
+      <c r="B270" t="n">
+        <v>14473998.93101005</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" t="n">
+        <v>75</v>
+      </c>
+      <c r="G270" t="n">
+        <v>4</v>
+      </c>
+      <c r="H270" t="n">
+        <v>2</v>
+      </c>
+      <c r="I270" t="n">
+        <v>23</v>
+      </c>
+      <c r="J270" t="n">
+        <v>9</v>
+      </c>
+      <c r="K270" t="n">
+        <v>2</v>
+      </c>
+      <c r="L270" t="n">
+        <v>3</v>
+      </c>
+      <c r="M270" t="n">
+        <v>4</v>
+      </c>
+      <c r="N270" t="n">
+        <v>4</v>
+      </c>
+      <c r="O270" t="n">
+        <v>3</v>
+      </c>
+      <c r="P270" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>10</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2</v>
+      </c>
+      <c r="S270" t="n">
+        <v>10</v>
+      </c>
+      <c r="T270" t="n">
+        <v>16</v>
+      </c>
+      <c r="U270" t="n">
+        <v>3</v>
+      </c>
+      <c r="V270" t="n">
+        <v>0</v>
+      </c>
+      <c r="W270" t="n">
+        <v>3</v>
+      </c>
+      <c r="X270" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31122,6 +31122,117 @@
       <c r="A271" s="1" t="n">
         <v>46283</v>
       </c>
+      <c r="B271" t="n">
+        <v>14328195.18153005</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" t="n">
+        <v>77</v>
+      </c>
+      <c r="G271" t="n">
+        <v>4</v>
+      </c>
+      <c r="H271" t="n">
+        <v>2</v>
+      </c>
+      <c r="I271" t="n">
+        <v>23</v>
+      </c>
+      <c r="J271" t="n">
+        <v>9</v>
+      </c>
+      <c r="K271" t="n">
+        <v>2</v>
+      </c>
+      <c r="L271" t="n">
+        <v>3</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>4</v>
+      </c>
+      <c r="O271" t="n">
+        <v>3</v>
+      </c>
+      <c r="P271" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>10</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2</v>
+      </c>
+      <c r="S271" t="n">
+        <v>11</v>
+      </c>
+      <c r="T271" t="n">
+        <v>16</v>
+      </c>
+      <c r="U271" t="n">
+        <v>3</v>
+      </c>
+      <c r="V271" t="n">
+        <v>0</v>
+      </c>
+      <c r="W271" t="n">
+        <v>3</v>
+      </c>
+      <c r="X271" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31238,6 +31238,117 @@
       <c r="A272" s="1" t="n">
         <v>46286</v>
       </c>
+      <c r="B272" t="n">
+        <v>14434239.65403005</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1</v>
+      </c>
+      <c r="F272" t="n">
+        <v>76</v>
+      </c>
+      <c r="G272" t="n">
+        <v>4</v>
+      </c>
+      <c r="H272" t="n">
+        <v>2</v>
+      </c>
+      <c r="I272" t="n">
+        <v>23</v>
+      </c>
+      <c r="J272" t="n">
+        <v>9</v>
+      </c>
+      <c r="K272" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" t="n">
+        <v>3</v>
+      </c>
+      <c r="M272" t="n">
+        <v>4</v>
+      </c>
+      <c r="N272" t="n">
+        <v>4</v>
+      </c>
+      <c r="O272" t="n">
+        <v>3</v>
+      </c>
+      <c r="P272" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>11</v>
+      </c>
+      <c r="R272" t="n">
+        <v>2</v>
+      </c>
+      <c r="S272" t="n">
+        <v>11</v>
+      </c>
+      <c r="T272" t="n">
+        <v>16</v>
+      </c>
+      <c r="U272" t="n">
+        <v>3</v>
+      </c>
+      <c r="V272" t="n">
+        <v>0</v>
+      </c>
+      <c r="W272" t="n">
+        <v>3</v>
+      </c>
+      <c r="X272" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31359,6 +31359,117 @@
       <c r="A274" s="1" t="n">
         <v>46288</v>
       </c>
+      <c r="B274" t="n">
+        <v>14479176.60443005</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" t="n">
+        <v>77</v>
+      </c>
+      <c r="G274" t="n">
+        <v>5</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2</v>
+      </c>
+      <c r="I274" t="n">
+        <v>23</v>
+      </c>
+      <c r="J274" t="n">
+        <v>9</v>
+      </c>
+      <c r="K274" t="n">
+        <v>1</v>
+      </c>
+      <c r="L274" t="n">
+        <v>3</v>
+      </c>
+      <c r="M274" t="n">
+        <v>4</v>
+      </c>
+      <c r="N274" t="n">
+        <v>4</v>
+      </c>
+      <c r="O274" t="n">
+        <v>3</v>
+      </c>
+      <c r="P274" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>11</v>
+      </c>
+      <c r="R274" t="n">
+        <v>2</v>
+      </c>
+      <c r="S274" t="n">
+        <v>11</v>
+      </c>
+      <c r="T274" t="n">
+        <v>16</v>
+      </c>
+      <c r="U274" t="n">
+        <v>3</v>
+      </c>
+      <c r="V274" t="n">
+        <v>0</v>
+      </c>
+      <c r="W274" t="n">
+        <v>3</v>
+      </c>
+      <c r="X274" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31475,6 +31475,117 @@
       <c r="A275" s="1" t="n">
         <v>46289</v>
       </c>
+      <c r="B275" t="n">
+        <v>14360032.05523005</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" t="n">
+        <v>80</v>
+      </c>
+      <c r="G275" t="n">
+        <v>6</v>
+      </c>
+      <c r="H275" t="n">
+        <v>2</v>
+      </c>
+      <c r="I275" t="n">
+        <v>25</v>
+      </c>
+      <c r="J275" t="n">
+        <v>9</v>
+      </c>
+      <c r="K275" t="n">
+        <v>2</v>
+      </c>
+      <c r="L275" t="n">
+        <v>3</v>
+      </c>
+      <c r="M275" t="n">
+        <v>4</v>
+      </c>
+      <c r="N275" t="n">
+        <v>4</v>
+      </c>
+      <c r="O275" t="n">
+        <v>3</v>
+      </c>
+      <c r="P275" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>11</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2</v>
+      </c>
+      <c r="S275" t="n">
+        <v>12</v>
+      </c>
+      <c r="T275" t="n">
+        <v>17</v>
+      </c>
+      <c r="U275" t="n">
+        <v>3</v>
+      </c>
+      <c r="V275" t="n">
+        <v>0</v>
+      </c>
+      <c r="W275" t="n">
+        <v>3</v>
+      </c>
+      <c r="X275" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31631,6 +31631,117 @@
       <c r="A284" s="1" t="n">
         <v>46310</v>
       </c>
+      <c r="B284" t="n">
+        <v>13656772.96848005</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1</v>
+      </c>
+      <c r="F284" t="n">
+        <v>70</v>
+      </c>
+      <c r="G284" t="n">
+        <v>6</v>
+      </c>
+      <c r="H284" t="n">
+        <v>2</v>
+      </c>
+      <c r="I284" t="n">
+        <v>23</v>
+      </c>
+      <c r="J284" t="n">
+        <v>9</v>
+      </c>
+      <c r="K284" t="n">
+        <v>1</v>
+      </c>
+      <c r="L284" t="n">
+        <v>3</v>
+      </c>
+      <c r="M284" t="n">
+        <v>4</v>
+      </c>
+      <c r="N284" t="n">
+        <v>4</v>
+      </c>
+      <c r="O284" t="n">
+        <v>3</v>
+      </c>
+      <c r="P284" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>10</v>
+      </c>
+      <c r="R284" t="n">
+        <v>2</v>
+      </c>
+      <c r="S284" t="n">
+        <v>10</v>
+      </c>
+      <c r="T284" t="n">
+        <v>16</v>
+      </c>
+      <c r="U284" t="n">
+        <v>3</v>
+      </c>
+      <c r="V284" t="n">
+        <v>0</v>
+      </c>
+      <c r="W284" t="n">
+        <v>3</v>
+      </c>
+      <c r="X284" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31747,6 +31747,117 @@
       <c r="A285" s="1" t="n">
         <v>46311</v>
       </c>
+      <c r="B285" t="n">
+        <v>13364812.66088005</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1</v>
+      </c>
+      <c r="F285" t="n">
+        <v>69</v>
+      </c>
+      <c r="G285" t="n">
+        <v>6</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" t="n">
+        <v>22</v>
+      </c>
+      <c r="J285" t="n">
+        <v>9</v>
+      </c>
+      <c r="K285" t="n">
+        <v>1</v>
+      </c>
+      <c r="L285" t="n">
+        <v>3</v>
+      </c>
+      <c r="M285" t="n">
+        <v>4</v>
+      </c>
+      <c r="N285" t="n">
+        <v>4</v>
+      </c>
+      <c r="O285" t="n">
+        <v>3</v>
+      </c>
+      <c r="P285" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>10</v>
+      </c>
+      <c r="R285" t="n">
+        <v>2</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="n">
+        <v>16</v>
+      </c>
+      <c r="U285" t="n">
+        <v>3</v>
+      </c>
+      <c r="V285" t="n">
+        <v>0</v>
+      </c>
+      <c r="W285" t="n">
+        <v>3</v>
+      </c>
+      <c r="X285" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31863,6 +31863,117 @@
       <c r="A286" s="1" t="n">
         <v>46314</v>
       </c>
+      <c r="B286" t="n">
+        <v>13529857.66088005</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1</v>
+      </c>
+      <c r="F286" t="n">
+        <v>68</v>
+      </c>
+      <c r="G286" t="n">
+        <v>6</v>
+      </c>
+      <c r="H286" t="n">
+        <v>2</v>
+      </c>
+      <c r="I286" t="n">
+        <v>22</v>
+      </c>
+      <c r="J286" t="n">
+        <v>9</v>
+      </c>
+      <c r="K286" t="n">
+        <v>1</v>
+      </c>
+      <c r="L286" t="n">
+        <v>3</v>
+      </c>
+      <c r="M286" t="n">
+        <v>4</v>
+      </c>
+      <c r="N286" t="n">
+        <v>4</v>
+      </c>
+      <c r="O286" t="n">
+        <v>3</v>
+      </c>
+      <c r="P286" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>10</v>
+      </c>
+      <c r="R286" t="n">
+        <v>2</v>
+      </c>
+      <c r="S286" t="n">
+        <v>10</v>
+      </c>
+      <c r="T286" t="n">
+        <v>16</v>
+      </c>
+      <c r="U286" t="n">
+        <v>3</v>
+      </c>
+      <c r="V286" t="n">
+        <v>0</v>
+      </c>
+      <c r="W286" t="n">
+        <v>3</v>
+      </c>
+      <c r="X286" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -31984,6 +31984,117 @@
       <c r="A288" s="1" t="n">
         <v>46316</v>
       </c>
+      <c r="B288" t="n">
+        <v>13686254.73368005</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" t="n">
+        <v>68</v>
+      </c>
+      <c r="G288" t="n">
+        <v>6</v>
+      </c>
+      <c r="H288" t="n">
+        <v>2</v>
+      </c>
+      <c r="I288" t="n">
+        <v>21</v>
+      </c>
+      <c r="J288" t="n">
+        <v>8</v>
+      </c>
+      <c r="K288" t="n">
+        <v>1</v>
+      </c>
+      <c r="L288" t="n">
+        <v>3</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>4</v>
+      </c>
+      <c r="O288" t="n">
+        <v>3</v>
+      </c>
+      <c r="P288" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>10</v>
+      </c>
+      <c r="R288" t="n">
+        <v>1</v>
+      </c>
+      <c r="S288" t="n">
+        <v>10</v>
+      </c>
+      <c r="T288" t="n">
+        <v>15</v>
+      </c>
+      <c r="U288" t="n">
+        <v>3</v>
+      </c>
+      <c r="V288" t="n">
+        <v>0</v>
+      </c>
+      <c r="W288" t="n">
+        <v>3</v>
+      </c>
+      <c r="X288" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -32100,6 +32100,117 @@
       <c r="A289" s="1" t="n">
         <v>46317</v>
       </c>
+      <c r="B289" t="n">
+        <v>13537889.61678005</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1</v>
+      </c>
+      <c r="F289" t="n">
+        <v>68</v>
+      </c>
+      <c r="G289" t="n">
+        <v>6</v>
+      </c>
+      <c r="H289" t="n">
+        <v>2</v>
+      </c>
+      <c r="I289" t="n">
+        <v>22</v>
+      </c>
+      <c r="J289" t="n">
+        <v>9</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>3</v>
+      </c>
+      <c r="M289" t="n">
+        <v>4</v>
+      </c>
+      <c r="N289" t="n">
+        <v>4</v>
+      </c>
+      <c r="O289" t="n">
+        <v>3</v>
+      </c>
+      <c r="P289" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>10</v>
+      </c>
+      <c r="R289" t="n">
+        <v>1</v>
+      </c>
+      <c r="S289" t="n">
+        <v>10</v>
+      </c>
+      <c r="T289" t="n">
+        <v>15</v>
+      </c>
+      <c r="U289" t="n">
+        <v>3</v>
+      </c>
+      <c r="V289" t="n">
+        <v>0</v>
+      </c>
+      <c r="W289" t="n">
+        <v>3</v>
+      </c>
+      <c r="X289" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -32216,6 +32216,117 @@
       <c r="A290" s="1" t="n">
         <v>46318</v>
       </c>
+      <c r="B290" t="n">
+        <v>13361120.71278005</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1</v>
+      </c>
+      <c r="F290" t="n">
+        <v>66</v>
+      </c>
+      <c r="G290" t="n">
+        <v>6</v>
+      </c>
+      <c r="H290" t="n">
+        <v>2</v>
+      </c>
+      <c r="I290" t="n">
+        <v>22</v>
+      </c>
+      <c r="J290" t="n">
+        <v>9</v>
+      </c>
+      <c r="K290" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" t="n">
+        <v>3</v>
+      </c>
+      <c r="M290" t="n">
+        <v>4</v>
+      </c>
+      <c r="N290" t="n">
+        <v>4</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>10</v>
+      </c>
+      <c r="R290" t="n">
+        <v>1</v>
+      </c>
+      <c r="S290" t="n">
+        <v>10</v>
+      </c>
+      <c r="T290" t="n">
+        <v>16</v>
+      </c>
+      <c r="U290" t="n">
+        <v>3</v>
+      </c>
+      <c r="V290" t="n">
+        <v>0</v>
+      </c>
+      <c r="W290" t="n">
+        <v>3</v>
+      </c>
+      <c r="X290" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -32332,6 +32332,117 @@
       <c r="A291" s="1" t="n">
         <v>46321</v>
       </c>
+      <c r="B291" t="n">
+        <v>13406015.45238005</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1</v>
+      </c>
+      <c r="F291" t="n">
+        <v>65</v>
+      </c>
+      <c r="G291" t="n">
+        <v>6</v>
+      </c>
+      <c r="H291" t="n">
+        <v>2</v>
+      </c>
+      <c r="I291" t="n">
+        <v>21</v>
+      </c>
+      <c r="J291" t="n">
+        <v>8</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>3</v>
+      </c>
+      <c r="M291" t="n">
+        <v>4</v>
+      </c>
+      <c r="N291" t="n">
+        <v>4</v>
+      </c>
+      <c r="O291" t="n">
+        <v>3</v>
+      </c>
+      <c r="P291" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>10</v>
+      </c>
+      <c r="R291" t="n">
+        <v>1</v>
+      </c>
+      <c r="S291" t="n">
+        <v>9</v>
+      </c>
+      <c r="T291" t="n">
+        <v>14</v>
+      </c>
+      <c r="U291" t="n">
+        <v>2</v>
+      </c>
+      <c r="V291" t="n">
+        <v>0</v>
+      </c>
+      <c r="W291" t="n">
+        <v>3</v>
+      </c>
+      <c r="X291" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
